--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -631,22 +631,22 @@
         <v>110.45</v>
       </c>
       <c r="C2" t="n">
-        <v>114.1</v>
+        <v>114.4</v>
       </c>
       <c r="D2" t="n">
         <v>110.45</v>
       </c>
       <c r="E2" t="n">
-        <v>114.05</v>
+        <v>112.6</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0335</v>
+        <v>0.0204</v>
       </c>
       <c r="H2" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="I2" t="n">
         <v>101.25</v>
@@ -679,15 +679,11 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U2" s="6" t="inlineStr"/>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
+      <c r="V2" s="6" t="inlineStr"/>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -637,13 +637,13 @@
         <v>110.45</v>
       </c>
       <c r="E2" t="n">
-        <v>112.6</v>
+        <v>113.55</v>
       </c>
       <c r="F2" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0204</v>
+        <v>0.029</v>
       </c>
       <c r="H2" t="n">
         <v>3.95</v>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -637,13 +637,13 @@
         <v>110.45</v>
       </c>
       <c r="E2" t="n">
-        <v>113.55</v>
+        <v>113.05</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.029</v>
+        <v>0.0245</v>
       </c>
       <c r="H2" t="n">
         <v>3.95</v>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -637,13 +637,13 @@
         <v>110.45</v>
       </c>
       <c r="E2" t="n">
-        <v>113.05</v>
+        <v>112.65</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0245</v>
+        <v>0.0208</v>
       </c>
       <c r="H2" t="n">
         <v>3.95</v>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -637,13 +637,13 @@
         <v>110.45</v>
       </c>
       <c r="E2" t="n">
-        <v>112.65</v>
+        <v>112.8</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0222</v>
       </c>
       <c r="H2" t="n">
         <v>3.95</v>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -691,6 +691,78 @@
       </c>
       <c r="X2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>112.05</v>
+      </c>
+      <c r="E3" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I3" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>109.04</v>
+      </c>
+      <c r="K3" t="n">
+        <v>110.83</v>
+      </c>
+      <c r="L3" t="n">
+        <v>112.61</v>
+      </c>
+      <c r="M3" t="n">
+        <v>114.78</v>
+      </c>
+      <c r="N3" t="n">
+        <v>116.94</v>
+      </c>
+      <c r="O3" t="n">
+        <v>118.35</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr"/>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="6" t="inlineStr"/>
+      <c r="V3" s="6" t="inlineStr"/>
+      <c r="W3" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -701,22 +701,22 @@
         <v>112.5</v>
       </c>
       <c r="C3" t="n">
-        <v>113.1</v>
+        <v>113.55</v>
       </c>
       <c r="D3" t="n">
-        <v>112.05</v>
+        <v>111.45</v>
       </c>
       <c r="E3" t="n">
-        <v>112.65</v>
+        <v>113.2</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.15</v>
+        <v>0.4</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0035</v>
       </c>
       <c r="H3" t="n">
-        <v>1.05</v>
+        <v>2.1</v>
       </c>
       <c r="I3" t="n">
         <v>106.5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -707,13 +707,13 @@
         <v>111.45</v>
       </c>
       <c r="E3" t="n">
-        <v>113.2</v>
+        <v>112.9</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0009</v>
       </c>
       <c r="H3" t="n">
         <v>2.1</v>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -701,22 +701,22 @@
         <v>112.5</v>
       </c>
       <c r="C3" t="n">
-        <v>113.55</v>
+        <v>113.6</v>
       </c>
       <c r="D3" t="n">
         <v>111.45</v>
       </c>
       <c r="E3" t="n">
-        <v>112.9</v>
+        <v>113.25</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.004</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="I3" t="n">
         <v>106.5</v>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -707,13 +707,13 @@
         <v>111.45</v>
       </c>
       <c r="E3" t="n">
-        <v>113.25</v>
+        <v>113.3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0044</v>
       </c>
       <c r="H3" t="n">
         <v>2.15</v>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -682,8 +682,12 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="6" t="inlineStr"/>
-      <c r="V2" s="6" t="inlineStr"/>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
+      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
@@ -750,8 +754,12 @@
       <c r="T3" s="8" t="n">
         <v/>
       </c>
-      <c r="U3" s="6" t="inlineStr"/>
-      <c r="V3" s="6" t="inlineStr"/>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
+      </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
@@ -762,6 +770,84 @@
           <t>弱警訊</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>111.54</v>
+      </c>
+      <c r="K4" t="n">
+        <v>112.22</v>
+      </c>
+      <c r="L4" t="n">
+        <v>112.91</v>
+      </c>
+      <c r="M4" t="n">
+        <v>114.37</v>
+      </c>
+      <c r="N4" t="n">
+        <v>115.84</v>
+      </c>
+      <c r="O4" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr"/>
+      <c r="Q4" s="6" t="inlineStr"/>
+      <c r="R4" s="6" t="inlineStr"/>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W4" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -781,22 +781,22 @@
         <v>115.2</v>
       </c>
       <c r="C4" t="n">
-        <v>117.5</v>
+        <v>117.65</v>
       </c>
       <c r="D4" t="n">
         <v>115.2</v>
       </c>
       <c r="E4" t="n">
-        <v>117.3</v>
+        <v>117.05</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.0331</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="I4" t="n">
         <v>109.3</v>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -784,19 +784,19 @@
         <v>117.65</v>
       </c>
       <c r="D4" t="n">
-        <v>115.2</v>
+        <v>115</v>
       </c>
       <c r="E4" t="n">
-        <v>117.05</v>
+        <v>115.7</v>
       </c>
       <c r="F4" t="n">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0331</v>
+        <v>0.0212</v>
       </c>
       <c r="H4" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="I4" t="n">
         <v>109.3</v>
@@ -834,12 +834,12 @@
       </c>
       <c r="U4" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W4" s="9" t="inlineStr">

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -784,19 +784,19 @@
         <v>117.65</v>
       </c>
       <c r="D4" t="n">
-        <v>115</v>
+        <v>114.9</v>
       </c>
       <c r="E4" t="n">
-        <v>115.7</v>
+        <v>114.9</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0212</v>
+        <v>0.0141</v>
       </c>
       <c r="H4" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="I4" t="n">
         <v>109.3</v>
@@ -829,17 +829,17 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W4" s="9" t="inlineStr">

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+0.00%;-0.00%;0.00%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -80,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,13 +104,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -470,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -671,24 +683,26 @@
       </c>
       <c r="P2" s="6" t="inlineStr"/>
       <c r="Q2" s="6" t="inlineStr"/>
-      <c r="R2" s="6" t="inlineStr"/>
-      <c r="S2" s="7" t="inlineStr">
+      <c r="R2" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
+      <c r="T2" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W2" s="9" t="inlineStr">
+      <c r="U2" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W2" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -745,22 +759,24 @@
       </c>
       <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="7" t="inlineStr">
+      <c r="R3" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="8" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="T3" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W3" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -821,33 +837,115 @@
       </c>
       <c r="P4" s="6" t="inlineStr"/>
       <c r="Q4" s="6" t="inlineStr"/>
-      <c r="R4" s="6" t="inlineStr"/>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="R4" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="T4" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="U4" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V4" s="8" t="inlineStr">
+      <c r="V4" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="W4" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-0.0113</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>112.15</v>
+      </c>
+      <c r="J5" t="n">
+        <v>111.46</v>
+      </c>
+      <c r="K5" t="n">
+        <v>113.53</v>
+      </c>
+      <c r="L5" t="n">
+        <v>115.59</v>
+      </c>
+      <c r="M5" t="n">
+        <v>116.28</v>
+      </c>
+      <c r="N5" t="n">
+        <v>116.96</v>
+      </c>
+      <c r="O5" t="n">
+        <v>120.4</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr"/>
+      <c r="Q5" s="6" t="inlineStr"/>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S5" s="11" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="10" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -874,25 +874,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>114.2</v>
+        <v>113.6</v>
       </c>
       <c r="C5" t="n">
-        <v>114.7</v>
+        <v>115.2</v>
       </c>
       <c r="D5" t="n">
-        <v>112.9</v>
+        <v>113.6</v>
       </c>
       <c r="E5" t="n">
-        <v>113.6</v>
+        <v>113.8</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0113</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="I5" t="n">
         <v>112.15</v>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -101,10 +101,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -681,9 +681,11 @@
       <c r="O2" t="n">
         <v>115.05</v>
       </c>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="6" t="inlineStr"/>
-      <c r="R2" s="7" t="n">
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="7" t="inlineStr"/>
+      <c r="R2" s="6" t="n">
         <v/>
       </c>
       <c r="S2" s="8" t="inlineStr">
@@ -757,9 +759,11 @@
       <c r="O3" t="n">
         <v>118.35</v>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="7" t="n">
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="7" t="inlineStr"/>
+      <c r="R3" s="6" t="n">
         <v/>
       </c>
       <c r="S3" s="8" t="inlineStr">
@@ -835,9 +839,11 @@
       <c r="O4" t="n">
         <v>115.75</v>
       </c>
-      <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr"/>
-      <c r="R4" s="7" t="n">
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="7" t="inlineStr"/>
+      <c r="R4" s="6" t="n">
         <v/>
       </c>
       <c r="S4" s="8" t="inlineStr">
@@ -880,19 +886,19 @@
         <v>115.2</v>
       </c>
       <c r="D5" t="n">
-        <v>113.6</v>
+        <v>112.1</v>
       </c>
       <c r="E5" t="n">
-        <v>113.8</v>
+        <v>113.3</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0139</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
         <v>112.15</v>
@@ -915,9 +921,13 @@
       <c r="O5" t="n">
         <v>120.4</v>
       </c>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="6" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr">
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr"/>
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -104,9 +104,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -117,6 +114,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -684,27 +682,29 @@
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="7" t="inlineStr"/>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
       <c r="R2" s="6" t="n">
         <v/>
       </c>
-      <c r="S2" s="8" t="inlineStr">
+      <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T2" s="9" t="inlineStr">
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W2" s="10" t="inlineStr">
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -762,25 +762,27 @@
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="7" t="inlineStr"/>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T3" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -842,31 +844,33 @@
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="7" t="inlineStr"/>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T4" s="9" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U4" s="9" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V4" s="9" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -886,19 +890,19 @@
         <v>115.2</v>
       </c>
       <c r="D5" t="n">
-        <v>112.1</v>
+        <v>111.2</v>
       </c>
       <c r="E5" t="n">
-        <v>113.3</v>
+        <v>111.35</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6</v>
+        <v>-3.55</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.0309</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>112.15</v>
@@ -926,36 +930,36 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q5" s="7" t="inlineStr"/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S5" s="11" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T5" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W5" s="10" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -890,19 +890,19 @@
         <v>115.2</v>
       </c>
       <c r="D5" t="n">
-        <v>111.2</v>
+        <v>107.1</v>
       </c>
       <c r="E5" t="n">
-        <v>111.35</v>
+        <v>109.4</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.55</v>
+        <v>-5.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0309</v>
+        <v>-0.0479</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>8.1</v>
       </c>
       <c r="I5" t="n">
         <v>112.15</v>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -893,13 +893,13 @@
         <v>107.1</v>
       </c>
       <c r="E5" t="n">
-        <v>109.4</v>
+        <v>109.2</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.5</v>
+        <v>-5.7</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0479</v>
+        <v>-0.0496</v>
       </c>
       <c r="H5" t="n">
         <v>8.1</v>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -961,6 +961,86 @@
       </c>
       <c r="X5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="C6" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="E6" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-0.0243</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I6" t="n">
+        <v>99</v>
+      </c>
+      <c r="J6" t="n">
+        <v>100.13</v>
+      </c>
+      <c r="K6" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="L6" t="n">
+        <v>110.18</v>
+      </c>
+      <c r="M6" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="N6" t="n">
+        <v>116.33</v>
+      </c>
+      <c r="O6" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -968,25 +968,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>109.15</v>
+        <v>106.8</v>
       </c>
       <c r="C6" t="n">
-        <v>109.2</v>
+        <v>109</v>
       </c>
       <c r="D6" t="n">
-        <v>106.25</v>
+        <v>106.75</v>
       </c>
       <c r="E6" t="n">
-        <v>106.55</v>
+        <v>108.35</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.65</v>
+        <v>-0.85</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0243</v>
+        <v>-0.0078</v>
       </c>
       <c r="H6" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="I6" t="n">
         <v>99</v>
@@ -1015,14 +1015,12 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -977,13 +977,13 @@
         <v>106.75</v>
       </c>
       <c r="E6" t="n">
-        <v>108.35</v>
+        <v>108.75</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.85</v>
+        <v>-0.45</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0041</v>
       </c>
       <c r="H6" t="n">
         <v>2.25</v>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -971,22 +971,22 @@
         <v>106.8</v>
       </c>
       <c r="C6" t="n">
-        <v>109</v>
+        <v>110.05</v>
       </c>
       <c r="D6" t="n">
         <v>106.75</v>
       </c>
       <c r="E6" t="n">
-        <v>108.75</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.45</v>
+        <v>0.8</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0073</v>
       </c>
       <c r="H6" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="I6" t="n">
         <v>99</v>
@@ -1037,7 +1037,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -974,19 +974,19 @@
         <v>110.05</v>
       </c>
       <c r="D6" t="n">
-        <v>106.75</v>
+        <v>105.05</v>
       </c>
       <c r="E6" t="n">
-        <v>110</v>
+        <v>105.1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8</v>
+        <v>-4.1</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0375</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
         <v>99</v>
@@ -1015,12 +1015,14 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1037,11 +1039,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1041,6 +1041,84 @@
       </c>
       <c r="X6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="C7" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="D7" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="E7" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="J7" t="n">
+        <v>98.87</v>
+      </c>
+      <c r="K7" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>106.32</v>
+      </c>
+      <c r="M7" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="N7" t="n">
+        <v>108.87</v>
+      </c>
+      <c r="O7" t="n">
+        <v>115.05</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>106.65</v>
+        <v>107.1</v>
       </c>
       <c r="C7" t="n">
-        <v>107.15</v>
+        <v>108.4</v>
       </c>
       <c r="D7" t="n">
-        <v>105.05</v>
+        <v>106.1</v>
       </c>
       <c r="E7" t="n">
-        <v>105.1</v>
+        <v>108.3</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0</v>
+        <v>0.0304</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="I7" t="n">
         <v>100.05</v>
@@ -1098,16 +1098,20 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1117,7 +1121,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -1051,22 +1051,22 @@
         <v>107.1</v>
       </c>
       <c r="C7" t="n">
-        <v>108.4</v>
+        <v>109.5</v>
       </c>
       <c r="D7" t="n">
         <v>106.1</v>
       </c>
       <c r="E7" t="n">
-        <v>108.3</v>
+        <v>108.7</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0304</v>
+        <v>0.0343</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="I7" t="n">
         <v>100.05</v>

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -1057,13 +1057,13 @@
         <v>106.1</v>
       </c>
       <c r="E7" t="n">
-        <v>108.7</v>
+        <v>106.35</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0343</v>
+        <v>0.0119</v>
       </c>
       <c r="H7" t="n">
         <v>3.4</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="U7" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V7" s="8" t="n">

--- a/three_gate/analysis/T5F_weekly.xlsx
+++ b/three_gate/analysis/T5F_weekly.xlsx
@@ -1054,19 +1054,19 @@
         <v>109.5</v>
       </c>
       <c r="D7" t="n">
-        <v>106.1</v>
+        <v>104</v>
       </c>
       <c r="E7" t="n">
-        <v>106.35</v>
+        <v>104.85</v>
       </c>
       <c r="F7" t="n">
-        <v>1.25</v>
+        <v>-0.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0119</v>
+        <v>-0.0024</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="I7" t="n">
         <v>100.05</v>
@@ -1098,9 +1098,9 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
@@ -1121,11 +1121,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
